--- a/בדיקות.xlsx
+++ b/בדיקות.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\לימודי תוכנה\פרוייקט\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23393c4c06a5064/Documents/GitHub/CyberWall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673FEC3B-FDE1-4AC2-848A-919A642ED7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{673FEC3B-FDE1-4AC2-848A-919A642ED7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21DB0F4F-6E83-4632-A0C4-E023D27E16E8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C57CE70E-8465-44E8-917D-32E9519256A1}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8964" xr2:uid="{C57CE70E-8465-44E8-917D-32E9519256A1}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,36 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>מספר מזהה</t>
   </si>
@@ -178,7 +199,16 @@
     <t xml:space="preserve">1 בדיקת כי אכן המשתמש יכול להוסיף או להסיר הרשאות </t>
   </si>
   <si>
-    <t>לחיצה על כתפור ל</t>
+    <t>לחיצה על כתפור לאישור הרשאות למצלמה</t>
+  </si>
+  <si>
+    <t>לחיצה על כתפור לאישור הרשאות למיקרופון</t>
+  </si>
+  <si>
+    <t>בדיקה כי המיקרופון והמצלמה פועלים באפליקציות המבקשות אישור</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> לחיצה על כפתור להרשאות WIFI באפליקציה</t>
   </si>
 </sst>
 </file>
@@ -430,42 +460,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -817,7 +847,7 @@
       <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="13" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -827,180 +857,189 @@
       <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="4" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>1.2</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
+      <c r="A5" s="14">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
+      <c r="A6" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="18"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6" ht="69" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
+      <c r="A7" s="14">
         <v>1.2</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="18"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
+      <c r="A8" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="18"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
+      <c r="A9" s="14">
         <v>1.2</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="18"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
+      <c r="A10" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">C15:AL16</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
